--- a/StatsWithPython.xlsx
+++ b/StatsWithPython.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
   <si>
     <t>Topic</t>
   </si>
@@ -232,13 +232,16 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1GjrnkYc1tEgK2uGgqaKRZeBQ2UtrVJYZ?usp=sharing</t>
+  </si>
+  <si>
+    <t>AI Related</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +272,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -294,11 +304,12 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -742,6 +753,11 @@
         <v>32</v>
       </c>
     </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="23" spans="1:2" ht="15.75">
       <c r="A23" s="3" t="s">
         <v>33</v>
